--- a/Games/Microsoft Excel-Arbeitsblatt (neu).xlsx
+++ b/Games/Microsoft Excel-Arbeitsblatt (neu).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\GameMaster\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\GameMaster\Games\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3DD80FF-7723-4725-A5D1-BF5A860050FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02F31C4A-CCB5-4C4E-9787-8745B4D510F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -371,7 +371,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
@@ -536,6 +536,104 @@
         <v>Betreuer</v>
       </c>
     </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D9">
+        <f t="shared" ref="D9:D15" si="3">ABS($A9-B9)</f>
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <f t="shared" ref="E9:E15" si="4">ABS($A9-C9)</f>
+        <v>0</v>
+      </c>
+      <c r="F9" t="str">
+        <f t="shared" ref="F9:F15" si="5">IF(D9&lt;E9, $D$2,$E$2)</f>
+        <v>Betreuer</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D10">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F10" t="str">
+        <f t="shared" si="5"/>
+        <v>Betreuer</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F11" t="str">
+        <f t="shared" si="5"/>
+        <v>Betreuer</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D12">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F12" t="str">
+        <f t="shared" si="5"/>
+        <v>Betreuer</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F13" t="str">
+        <f t="shared" si="5"/>
+        <v>Betreuer</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D14">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F14" t="str">
+        <f t="shared" si="5"/>
+        <v>Betreuer</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D15">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F15" t="str">
+        <f t="shared" si="5"/>
+        <v>Betreuer</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
